--- a/public/crawlability-bth-september-2026.xlsx
+++ b/public/crawlability-bth-september-2026.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של bth ב-SE Ranking (הסריקה האחרונה: 2026-07-07).</t>
+          <t>להריץ מחדש את ה-Website Audit של bth ב-SE Ranking (הסריקה האחרונה: 2026-07-07); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. לא נמצא עמוד חלופי מובהק; אם קיים, להגדיר הפניית 301 (יעד לאישור). כתובת דוא"ל שנכתבה כקישור יחסי בעמוד /info/. לתקן ל-mailto:servicebth@bth.co.il; אין להגדיר הפניה.</t>
+          <t>כתובת דוא"ל שנכתבה כקישור יחסי בעמוד /info/. לתקן ל-mailto:servicebth@bth.co.il; אין להגדיר הפניה.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
@@ -1075,9 +1075,9 @@
           <t>https://www.bth.co.il/contact-us/</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת http שמפנה ל-https. לעדכן את הקישור לכתובת ה-https.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת http שמפנה ל-https. לעדכן את הקישור לכתובת ה-https.</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">

--- a/public/crawlability-bth-september-2026.xlsx
+++ b/public/crawlability-bth-september-2026.xlsx
@@ -8,12 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום פעולות" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="404 ושגיאות" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -526,7 +525,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>לתקן 12 עמודים במפת האתר שמחזירים 200 עם גוף שגיאה, או להסירם מהמפה.</t>
+          <t>לתקן 11 עמודים במפת האתר שמחזירים 200 עם גוף שגיאה, או להסירם מהמפה.</t>
         </is>
       </c>
     </row>
@@ -541,7 +540,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): כתובת אחת (הבולטת: https://www.bth.co.il/info/servicebth@bth.co.il, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת (הבולטת: https://www.bth.co.il/info/servicebth@bth.co.il, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -586,7 +585,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): 3 כתובות (הבולטת: https://www.bth.co.il/internal-product-page-הצהרת-נגישות, 101 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות זמניות (302/307): 2 כתובות (הבולטת: https://www.bth.co.il/internal-product-page-הצהרת-נגישות, 101 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -594,14 +593,14 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית: כתובת אחת (הבולטת: http://www.bth.co.il/, 0 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>debt.bth.co.il: להגדיר noindex או להסיר.</t>
         </is>
       </c>
     </row>
@@ -616,7 +615,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>debt.bth.co.il: להגדיר noindex או להסיר.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 2 כתובות (הבולטת: https://www.bth.co.il/info, 4 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -630,21 +629,6 @@
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 2 כתובות (הבולטת: https://www.bth.co.il/info, 4 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>להריץ מחדש את ה-Website Audit של bth ב-SE Ranking (הסריקה האחרונה: 2026-07-07); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
         </is>
@@ -656,437 +640,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>כתובת</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בסריקה 23.09</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בבדיקה חיה 27.09</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>יעד סופי / יעד להפניה</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>קפיצות</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>קישורים נכנסים</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>עמודי מקור (עד 10)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>סוג</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה נדרשת</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>יעד מומלץ להפניית 301</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/info/servicebth@bth.co.il</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/info/</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>כתובת דוא"ל שנכתבה כקישור יחסי בעמוד /info/. לתקן ל-mailto:servicebth@bth.co.il; אין להגדיר הפניה.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>כתובת</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בסריקה 23.09</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בבדיקה חיה 27.09</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>יעד סופי / יעד להפניה</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>קפיצות</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>קישורים נכנסים</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>עמודי מקור (עד 10)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>סוג</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה נדרשת</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>יעד מומלץ להפניית 301</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/contact</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/contact-us/</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/
-https://www.bth.co.il/responsible/
-https://www.bth.co.il/kibutz-sea/
-https://www.bth.co.il/exists-insurance/
-https://www.bth.co.il/forms/
-https://www.bth.co.il/contact-us/
-https://www.bth.co.il/house-claim-2/
-https://www.bth.co.il/abroad-claim/
-https://www.bth.co.il/car-hova/
-https://www.bth.co.il/terms/
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>שרשראות הפניות</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>שרשרת של 2 הפניות. להגדיר הפניה ישירה ליעד הסופי ולעדכן את הקישורים הפנימיים אליו.</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/contact-us/</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/internal-product-page-הצהרת-נגישות</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>302 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/accessibility/</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/
-https://www.bth.co.il/responsible/
-https://www.bth.co.il/kibutz-sea/
-https://www.bth.co.il/exists-insurance/
-https://www.bth.co.il/forms/
-https://www.bth.co.il/contact-us/
-https://www.bth.co.il/house-claim-2/
-https://www.bth.co.il/abroad-claim/
-https://www.bth.co.il/car-hova/
-https://www.bth.co.il/terms/
-(ועוד 40)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>הפניות זמניות (302/307)</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/accessibility/</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/check-insurance/</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>302 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/insurance-check/</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/car/</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>הפניות זמניות (302/307)</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/insurance-check/</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/home-page/contact/</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>302</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>302 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/contact-us/</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>הפניות זמניות (302/307)</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/contact-us/</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1168,7 +721,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>http://www.bth.co.il/</t>
+          <t>https://www.bth.co.il/contact</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
@@ -1181,140 +734,160 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/</t>
+          <t>https://www.bth.co.il/contact-us/</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+        <v>101</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/
+https://www.bth.co.il/responsible/
+https://www.bth.co.il/kibutz-sea/
+https://www.bth.co.il/exists-insurance/
+https://www.bth.co.il/forms/
+https://www.bth.co.il/contact-us/
+https://www.bth.co.il/house-claim-2/
+https://www.bth.co.il/abroad-claim/
+https://www.bth.co.il/car-hova/
+https://www.bth.co.il/terms/
+(ועוד 40)</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לגרסת דומיין לא קנונית</t>
+          <t>שרשראות הפניות</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת http שמפנה ל-https. לעדכן את הקישור לכתובת ה-https.</t>
+          <t>שרשרת של 2 הפניות. להגדיר הפניה ישירה ליעד הסופי ולעדכן את הקישורים הפנימיים אליו.</t>
         </is>
       </c>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+          <t>https://www.bth.co.il/contact-us/</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/info</t>
+          <t>https://www.bth.co.il/internal-product-page-הצהרת-נגישות</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>301 -&gt; 200</t>
+          <t>302 -&gt; 200</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/info/</t>
+          <t>https://www.bth.co.il/accessibility/</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/claim-mycar-other/
-https://www.bth.co.il/claim-mycar-bodydamage/
-https://www.bth.co.il/claim-mycar/
-https://www.bth.co.il/claim-my-car-stolen/</t>
+          <t>https://www.bth.co.il/
+https://www.bth.co.il/responsible/
+https://www.bth.co.il/kibutz-sea/
+https://www.bth.co.il/exists-insurance/
+https://www.bth.co.il/forms/
+https://www.bth.co.il/contact-us/
+https://www.bth.co.il/house-claim-2/
+https://www.bth.co.il/abroad-claim/
+https://www.bth.co.il/car-hova/
+https://www.bth.co.il/terms/
+(ועוד 40)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
+          <t>הפניות זמניות (302/307)</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/info/</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+          <t>https://www.bth.co.il/accessibility/</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/house-claim-2</t>
+          <t>https://www.bth.co.il/check-insurance/</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>301 -&gt; 200</t>
+          <t>302 -&gt; 200</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/house-claim-2/</t>
+          <t>https://www.bth.co.il/insurance-check/</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/home-mortgage/
-https://www.bth.co.il/home-content/</t>
+          <t>https://www.bth.co.il/car/</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
+          <t>הפניות זמניות (302/307)</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/house-claim-2/</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+          <t>https://www.bth.co.il/insurance-check/</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
     </row>
@@ -1323,13 +896,203 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>כתובת</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בסריקה 23.09</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בבדיקה חיה 27.09</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>יעד סופי / יעד להפניה</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>קפיצות</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>קישורים נכנסים</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>עמודי מקור (עד 10)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>סוג</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>פעולה נדרשת</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>יעד מומלץ להפניית 301</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>עדיפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/info</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/info/</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/claim-mycar-other/
+https://www.bth.co.il/claim-mycar-bodydamage/
+https://www.bth.co.il/claim-mycar/
+https://www.bth.co.il/claim-my-car-stolen/</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/info/</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/house-claim-2</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/house-claim-2/</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/home-mortgage/
+https://www.bth.co.il/home-content/</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>קישור פנימי לכתובת ללא לוכסן סופי (או עם), שמפנה לגרסה הקנונית. לעדכן את הקישור לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/house-claim-2/</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2276,15 +2039,19 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>גוף שגיאה (200 קצר)</t>
+          <t>מפנה</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/banners/</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>https://www.bth.co.il/home-page/contact/</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/contact-us/</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2299,12 +2066,12 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/home-page/contact/</t>
+          <t>https://www.bth.co.il/check-insurance/</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/contact-us/</t>
+          <t>https://www.bth.co.il/insurance-check/</t>
         </is>
       </c>
     </row>
@@ -2316,19 +2083,15 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>מפנה</t>
+          <t>קוד 301 (סריקה 23.09)</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/check-insurance/</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/insurance-check/</t>
-        </is>
-      </c>
+          <t>https://www.bth.co.il/info/</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2343,7 +2106,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/info/</t>
+          <t>https://www.bth.co.il/house-claim-2/</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -2361,7 +2124,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/house-claim-2/</t>
+          <t>https://www.bth.co.il/</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -2369,20 +2132,24 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>מפת אתר: כתובת לתיקון</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>קוד 301 (סריקה 23.09)</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
+          <t>גרסאות דומיין</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>https://www.bth.co.il/</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/ (0 הפניות)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2392,7 +2159,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/</t>
+          <t>http://www.bth.co.il/</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -2402,7 +2169,7 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>https://www.bth.co.il/ (0 הפניות)</t>
+          <t>https://www.bth.co.il/ (1 הפניות)</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2181,7 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>http://www.bth.co.il/</t>
+          <t>https://bth.co.il/</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -2436,7 +2203,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>https://bth.co.il/</t>
+          <t>http://bth.co.il/</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -2453,24 +2220,20 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>גרסאות דומיין</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>http://bth.co.il/</t>
+          <t>עמוד הבית</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>meta robots</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/ (1 הפניות)</t>
-        </is>
-      </c>
+          <t>לא מוגדר</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2480,12 +2243,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>meta robots</t>
+          <t>X-Robots-Tag</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>לא מוגדר</t>
+          <t>ללא</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2498,40 +2261,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>X-Robots-Tag</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>ללא</t>
+          <t>canonical</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>עמוד הבית</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>canonical</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bth.co.il/</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2704,7 +2449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/crawlability-bth-september-2026.xlsx
+++ b/public/crawlability-bth-september-2026.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J3" s="6" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>הפניה זמנית (302) לעמוד קיים. להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד.</t>
+          <t>הפניה זמנית (302) לעמוד קיים. אם ההפניה מכוונת וקבועה, להמיר להפניית 301 ליעד ולעדכן את הקישורים הפנימיים ישירות ליעד; אם הכתובת המקורית אמורה לחזור, לבטל את ההפניה.</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">

--- a/public/crawlability-bth-september-2026.xlsx
+++ b/public/crawlability-bth-september-2026.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="סיכום פעולות" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -540,7 +541,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת (הבולטת: https://www.bth.co.il/info/servicebth@bth.co.il, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): כתובת אחת; הבולטת https://www.bth.co.il/info/servicebth@bth.co.il (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -570,7 +571,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://www.bth.co.il/contact, 101 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: כתובת אחת; הבולטת https://www.bth.co.il/contact (101 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -585,7 +586,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>הפניות זמניות (302/307): 2 כתובות (הבולטת: https://www.bth.co.il/internal-product-page-הצהרת-נגישות, 101 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות זמניות (302/307): 2 כתובות; הבולטת https://www.bth.co.il/internal-product-page-הצהרת-נגישות (101 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -615,7 +616,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 2 כתובות (הבולטת: https://www.bth.co.il/info, 4 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים ללא לוכסן סופי: 2 כתובות; הבולטת https://www.bth.co.il/info (4 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -630,7 +631,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>להריץ מחדש את ה-Website Audit של bth ב-SE Ranking (הסריקה האחרונה: 2026-07-07); הפעלה מחדש דרך ה-API אינה זמינה בחשבון, יש להפעיל בממשק.</t>
+          <t>להריץ מחדש (בממשק) את ה-Website Audit של bth ב-SE Ranking; הסריקה האחרונה: 2026-07-07.</t>
         </is>
       </c>
     </row>
@@ -1092,6 +1093,184 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>כתובת</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בסריקה 23.09</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בבדיקה חיה 27.09</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>יעד סופי / יעד להפניה</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>קפיצות</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>קישורים נכנסים</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>עמודי מקור (עד 10)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>סוג</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>פעולה נדרשת</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>יעד מומלץ להפניית 301</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>עדיפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/home-page/contact/</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>302</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>302 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/contact-us/</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/contact-us/</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>http://www.bth.co.il/</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>https://www.bth.co.il/</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2276,7 +2455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2449,7 +2628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/crawlability-bth-september-2026.xlsx
+++ b/public/crawlability-bth-september-2026.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -556,7 +556,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר 27 כתובות שמפנות (301/302) ולהשאיר את כתובות היעד בלבד.</t>
+          <t>להסיר ממפת האתר 27 כתובות שמפנות (301/302) (באתר WordPress/Yoast: להעביר את העמודים המפנים לטיוטה או להחריגם מה-sitemap; המפה נוצרת אוטומטית).</t>
         </is>
       </c>
     </row>
@@ -601,37 +601,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>debt.bth.co.il: להגדיר noindex או להסיר.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
           <t>קישורים פנימיים ללא לוכסן סופי: 2 כתובות; הבולטת https://www.bth.co.il/info (4 קישורים נכנסים).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>להריץ מחדש (בממשק) את ה-Website Audit של bth ב-SE Ranking; הסריקה האחרונה: 2026-07-07.</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2552,72 +2522,6 @@
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>ללא</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>debt.bth.co.il</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>עמוד ריק</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>להגדיר noindex או להסיר.</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>my.bth.co.il</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>noindex,nofollow</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>אזור אישי, מוגן ב-noindex</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ללא פעולה.</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>ללא</t>
         </is>
